--- a/data/trans_orig/BARTHEL_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/BARTHEL_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>17789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34641</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23813</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46317</t>
+          <t>47978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274748</t>
+          <t>274794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>287087</t>
+          <t>287023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308293</t>
+          <t>308536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327117</t>
+          <t>326598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>589200</t>
+          <t>587539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611704</t>
+          <t>611070</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21168</t>
+          <t>21517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40605</t>
+          <t>41668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52213</t>
+          <t>52250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82211</t>
+          <t>83193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79434</t>
+          <t>78790</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>115372</t>
+          <t>116007</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169278</t>
+          <t>168215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188715</t>
+          <t>188366</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>251697</t>
+          <t>250715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>281695</t>
+          <t>281658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>428419</t>
+          <t>427784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464357</t>
+          <t>465001</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52301</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>75498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109071</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>109799</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153994</t>
+          <t>153159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450165</t>
+          <t>448530</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473284</t>
+          <t>471304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>567771</t>
+          <t>565643</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>603460</t>
+          <t>601344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1025314</t>
+          <t>1026149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069509</t>
+          <t>1068877</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16249</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>36172</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30499</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55745</t>
+          <t>57179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51906</t>
+          <t>52308</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84640</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274286</t>
+          <t>273614</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293537</t>
+          <t>293586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298251</t>
+          <t>296817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>323497</t>
+          <t>323297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>579142</t>
+          <t>579301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>611876</t>
+          <t>611474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45648</t>
+          <t>44268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75020</t>
+          <t>75491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131612</t>
+          <t>131588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171245</t>
+          <t>170900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>187253</t>
+          <t>185311</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234725</t>
+          <t>237426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>174831</t>
+          <t>174360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204203</t>
+          <t>205583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217734</t>
+          <t>218079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257367</t>
+          <t>257391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404105</t>
+          <t>401404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451577</t>
+          <t>453519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>102984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>171211</t>
+          <t>166780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219312</t>
+          <t>215353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>246971</t>
+          <t>247130</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309586</t>
+          <t>306910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>458396</t>
+          <t>456653</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>494362</t>
+          <t>492602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>523663</t>
+          <t>527622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>571764</t>
+          <t>576195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>993026</t>
+          <t>995702</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1055641</t>
+          <t>1055482</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>81,03%</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>12399</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>29641</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24260</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49351</t>
+          <t>46214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>67885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>304958</t>
+          <t>304689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>322696</t>
+          <t>321931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328411</t>
+          <t>331548</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>353502</t>
+          <t>353965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643325</t>
+          <t>644207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671769</t>
+          <t>671473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40183</t>
+          <t>39413</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63999</t>
+          <t>63167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114864</t>
+          <t>111988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159280</t>
+          <t>156082</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163044</t>
+          <t>161412</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>211214</t>
+          <t>212026</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192999</t>
+          <t>193831</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>216815</t>
+          <t>217585</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>240889</t>
+          <t>244087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>285305</t>
+          <t>288181</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>445953</t>
+          <t>445141</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>494123</t>
+          <t>495755</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56165</t>
+          <t>56185</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>145837</t>
+          <t>145972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198271</t>
+          <t>195591</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>210422</t>
+          <t>211551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267800</t>
+          <t>270154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,73%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>505276</t>
+          <t>505290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535163</t>
+          <t>535143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579660</t>
+          <t>582340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>632094</t>
+          <t>631959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1101459</t>
+          <t>1099105</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1158837</t>
+          <t>1157708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31776</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12686</t>
+          <t>28273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50218</t>
+          <t>45161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>55556</t>
+          <t>61177</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25886</t>
+          <t>50098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75661</t>
+          <t>73006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -4618,32 +4618,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>344103</t>
+          <t>381603</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>336389</t>
+          <t>372895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350911</t>
+          <t>388950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>574391</t>
+          <t>400745</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>555667</t>
+          <t>391284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>593199</t>
+          <t>408172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4688,32 +4688,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>918494</t>
+          <t>782347</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>898389</t>
+          <t>770518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>948164</t>
+          <t>793426</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -4731,17 +4731,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>605885</t>
+          <t>436445</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>605885</t>
+          <t>436445</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>605885</t>
+          <t>436445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>974050</t>
+          <t>843524</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>974050</t>
+          <t>843524</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>974050</t>
+          <t>843524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61049</t>
+          <t>64887</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51312</t>
+          <t>53454</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73272</t>
+          <t>76702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>156555</t>
+          <t>170882</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>142916</t>
+          <t>154957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>171516</t>
+          <t>186646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>217603</t>
+          <t>235770</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200796</t>
+          <t>216675</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>237144</t>
+          <t>255453</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -4961,32 +4961,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>219106</t>
+          <t>242266</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206883</t>
+          <t>230451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>228843</t>
+          <t>253699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>265370</t>
+          <t>289808</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>250409</t>
+          <t>274044</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>279009</t>
+          <t>305733</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5031,32 +5031,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>484476</t>
+          <t>532073</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>464935</t>
+          <t>512390</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>501283</t>
+          <t>551168</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5074,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>280155</t>
+          <t>307153</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>280155</t>
+          <t>307153</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>280155</t>
+          <t>307153</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>421925</t>
+          <t>460690</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>421925</t>
+          <t>460690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>421925</t>
+          <t>460690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>702079</t>
+          <t>767843</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>702079</t>
+          <t>767843</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>702079</t>
+          <t>767843</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>90364</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71839</t>
+          <t>75881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99136</t>
+          <t>105557</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>188049</t>
+          <t>206583</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100373</t>
+          <t>187084</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>241687</t>
+          <t>226763</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>273160</t>
+          <t>296947</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172260</t>
+          <t>272374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>320343</t>
+          <t>322447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>20,01%</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>563210</t>
+          <t>623868</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>549184</t>
+          <t>608675</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>576481</t>
+          <t>638351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>839761</t>
+          <t>690552</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>786123</t>
+          <t>670372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>927437</t>
+          <t>710051</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5374,32 +5374,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1402970</t>
+          <t>1314421</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1355787</t>
+          <t>1288921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1503870</t>
+          <t>1338994</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>648320</t>
+          <t>714232</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1027810</t>
+          <t>897135</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1676130</t>
+          <t>1611368</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
